--- a/investing/stock-etf-analysis/model/BBS_Valuation_Model_NVDA_META.xlsx
+++ b/investing/stock-etf-analysis/model/BBS_Valuation_Model_NVDA_META.xlsx
@@ -800,9 +800,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="397">
   <si>
     <t xml:space="preserve">Brand-to-Balance-Sheet (BBS) valuation model: NVIDIA and Meta Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brand-to-Balance-Sheet (BBS) method by Jay Nair · github.com/jay-nair-builds/toolkit</t>
   </si>
   <si>
     <t xml:space="preserve">Prices at close on 18 Sep 2026, USD billions unless stated. Education only: not personalised investment advice and not a recommendation to buy, sell or hold.</t>
@@ -2041,6 +2044,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FF595959"/>
@@ -2049,13 +2059,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -2174,6 +2177,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2186,15 +2193,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2207,10 +2214,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2230,7 +2233,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2246,15 +2249,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2262,23 +2265,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2286,15 +2289,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2302,19 +2305,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2322,11 +2325,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2334,11 +2337,11 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2350,11 +2353,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="175" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2366,11 +2369,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2386,11 +2389,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2646,7 +2649,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:B28"/>
+  <dimension ref="B1:B29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2664,121 +2667,126 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3"/>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3"/>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="3"/>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="B17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3"/>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="3" t="s">
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="3" t="s">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3"/>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="3" t="s">
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="2" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -2806,178 +2814,183 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="A4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>27</v>
       </c>
+      <c r="C5" s="11" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="12" t="n">
+      <c r="A6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="13" t="n">
         <f aca="false">NVDA!B5</f>
         <v>222.27</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <f aca="false">META!B5</f>
         <v>665.75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="13" t="n">
+      <c r="A7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="14" t="n">
         <f aca="false">NVDA!B27</f>
         <v>0.11</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="14" t="n">
         <f aca="false">META!B27</f>
         <v>0.0983660942879845</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="12" t="n">
+      <c r="A8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="13" t="n">
         <f aca="false">NVDA!C58</f>
         <v>55.7635470539218</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="13" t="n">
         <f aca="false">META!C58</f>
         <v>201.503593127538</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="12" t="n">
+      <c r="A9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="13" t="n">
         <f aca="false">NVDA!D58</f>
         <v>141.623455385411</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="13" t="n">
         <f aca="false">META!D58</f>
         <v>456.843177782755</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="12" t="n">
+      <c r="A10" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="13" t="n">
         <f aca="false">NVDA!E58</f>
         <v>238.703645158197</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="13" t="n">
         <f aca="false">META!E58</f>
         <v>722.46178400487</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="12" t="n">
+      <c r="A11" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="13" t="n">
         <f aca="false">NVDA!F58</f>
         <v>222.268084201378</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="13" t="n">
         <f aca="false">META!F58</f>
         <v>665.74354713072</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="14" t="n">
+      <c r="A12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="15" t="n">
         <f aca="false">NVDA!D60</f>
         <v>-0.36283144200562</v>
       </c>
-      <c r="C12" s="14" t="n">
+      <c r="C12" s="15" t="n">
         <f aca="false">META!D60</f>
         <v>-0.313791696909118</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="14" t="n">
+      <c r="A13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="15" t="n">
         <f aca="false">NVDA!D64</f>
         <v>0.2152044104052</v>
       </c>
-      <c r="C13" s="14" t="n">
+      <c r="C13" s="15" t="n">
         <f aca="false">META!D64</f>
         <v>0.118305390416613</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="14" t="n">
+      <c r="A14" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="15" t="n">
         <f aca="false">NVDA!F64</f>
         <v>0.317818231621242</v>
       </c>
-      <c r="C14" s="14" t="n">
+      <c r="C14" s="15" t="n">
         <f aca="false">META!F64</f>
         <v>0.187306078765982</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="14" t="n">
+      <c r="A15" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="15" t="n">
         <f aca="false">NVDA!D61</f>
         <v>0.511167687518758</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="15" t="n">
         <f aca="false">META!D61</f>
         <v>0.579734924712515</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="14" t="n">
+      <c r="A16" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="15" t="n">
         <f aca="false">NVDA!D63</f>
         <v>0.15</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="15" t="n">
         <f aca="false">META!D63</f>
         <v>0.12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>39</v>
+      <c r="A17" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="B17" s="16" t="n">
         <f aca="false">BBS_Score!B13</f>
@@ -2990,30 +3003,30 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="10" t="s">
+      <c r="A22" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="B22" s="11" t="s">
         <v>27</v>
       </c>
+      <c r="C22" s="11" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
-        <v>42</v>
+      <c r="A23" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="B23" s="17" t="n">
         <f aca="false">PE_Benchmarks!B10</f>
@@ -3025,8 +3038,8 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>43</v>
+      <c r="A24" s="12" t="s">
+        <v>44</v>
       </c>
       <c r="B24" s="17" t="n">
         <f aca="false">PE_Benchmarks!B18</f>
@@ -3038,8 +3051,8 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>44</v>
+      <c r="A25" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="B25" s="17" t="n">
         <f aca="false">PE_Benchmarks!B27</f>
@@ -3051,8 +3064,8 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>45</v>
+      <c r="A26" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="B26" s="17" t="n">
         <f aca="false">PE_Benchmarks!B41</f>
@@ -3064,27 +3077,27 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" s="14" t="n">
+      <c r="A27" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="15" t="n">
         <f aca="false">NVDA_PnL!B50</f>
         <v>0.668985818314878</v>
       </c>
-      <c r="C27" s="14" t="n">
+      <c r="C27" s="15" t="n">
         <f aca="false">META_PnL!B50</f>
         <v>0.185114151787598</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="14" t="n">
+      <c r="A28" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="15" t="n">
         <f aca="false">NVDA_PnL!B52</f>
         <v>0.2152044104052</v>
       </c>
-      <c r="C28" s="14" t="n">
+      <c r="C28" s="15" t="n">
         <f aca="false">META_PnL!B52</f>
         <v>0.118308330125378</v>
       </c>
@@ -3115,49 +3128,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="A4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>28</v>
+      <c r="A5" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>222.27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>51</v>
+      <c r="A6" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>5370</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>52</v>
+      <c r="A7" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="B7" s="20" t="n">
         <f aca="false">B6/B5</f>
@@ -3165,88 +3178,88 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>53</v>
+      <c r="A8" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="B8" s="19" t="n">
         <v>62.47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>54</v>
+      <c r="A9" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>38.86</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>55</v>
+      <c r="A10" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="B10" s="19" t="n">
         <v>302.97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>56</v>
+      <c r="A11" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="B11" s="21" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
+      <c r="A13" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>58</v>
+      <c r="A14" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="B14" s="22" t="n">
         <v>0.0494</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>59</v>
+      <c r="A15" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="B15" s="22" t="n">
         <v>0.045</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>60</v>
+      <c r="A16" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="B16" s="23" t="n">
         <v>2.22</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>61</v>
+      <c r="A17" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="B17" s="23" t="n">
         <v>0.67</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
-        <v>62</v>
+      <c r="A18" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="B18" s="24" t="n">
         <f aca="false">B17*B16+(1-B17)*1</f>
@@ -3254,8 +3267,8 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>63</v>
+      <c r="A19" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">B14+B18*B15</f>
@@ -3263,16 +3276,16 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>64</v>
+      <c r="A20" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="B20" s="22" t="n">
         <v>0.0575</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>65</v>
+      <c r="A21" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="B21" s="25" t="n">
         <f aca="false">B20*(1-B11)</f>
@@ -3280,8 +3293,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>66</v>
+      <c r="A22" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="B22" s="26" t="n">
         <f aca="false">B6/(B6+B9)</f>
@@ -3289,8 +3302,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
-        <v>67</v>
+      <c r="A23" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="B23" s="26" t="n">
         <f aca="false">B9/(B6+B9)</f>
@@ -3298,8 +3311,8 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>68</v>
+      <c r="A24" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">B22*B19+B23*B21</f>
@@ -3307,24 +3320,24 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>69</v>
+      <c r="A25" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="B25" s="27" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>70</v>
+      <c r="A26" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="B26" s="27" t="n">
         <v>0.11</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>29</v>
+      <c r="A27" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="B27" s="28" t="n">
         <f aca="false">MEDIAN(B25,B24,B26)</f>
@@ -3332,63 +3345,63 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
-        <v>71</v>
+      <c r="A28" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="B28" s="27" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>72</v>
+      <c r="A29" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="B29" s="27" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
+      <c r="A31" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="A32" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="B32" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="C32" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="D32" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="E32" s="11" t="s">
         <v>79</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C33" s="30"/>
       <c r="D33" s="30"/>
@@ -3403,10 +3416,10 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C34" s="30"/>
       <c r="D34" s="30"/>
@@ -3421,10 +3434,10 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C35" s="30"/>
       <c r="D35" s="30"/>
@@ -3439,10 +3452,10 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" s="30"/>
       <c r="D36" s="30"/>
@@ -3456,11 +3469,11 @@
       <c r="L36" s="30"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11" t="s">
-        <v>88</v>
+      <c r="A38" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" s="19" t="n">
         <v>400</v>
@@ -3477,11 +3490,11 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="11" t="s">
-        <v>90</v>
+      <c r="A39" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" s="21" t="n">
         <v>0.05</v>
@@ -3498,11 +3511,11 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="C40" s="21" t="n">
         <v>-0.1</v>
@@ -3519,11 +3532,11 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
-        <v>93</v>
+      <c r="A41" s="12" t="s">
+        <v>94</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" s="21" t="n">
         <v>0</v>
@@ -3540,11 +3553,11 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
-        <v>94</v>
+      <c r="A42" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C42" s="21" t="n">
         <v>0.03</v>
@@ -3561,11 +3574,11 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11" t="s">
-        <v>95</v>
+      <c r="A43" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C43" s="21" t="n">
         <v>0.55</v>
@@ -3582,11 +3595,11 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>96</v>
+      <c r="A44" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C44" s="21" t="n">
         <v>0.45</v>
@@ -3603,11 +3616,11 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
-        <v>97</v>
+      <c r="A45" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C45" s="21" t="n">
         <v>0.75</v>
@@ -3624,11 +3637,11 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="s">
-        <v>98</v>
+      <c r="A46" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C46" s="21" t="n">
         <v>0.75</v>
@@ -3645,11 +3658,11 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11" t="s">
-        <v>99</v>
+      <c r="A47" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C47" s="32" t="n">
         <v>1</v>
@@ -3664,51 +3677,51 @@
         <v>1.8041</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
+      <c r="A49" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" s="10" t="s">
+      <c r="A50" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="C50" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="D50" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="E50" s="11" t="s">
         <v>79</v>
       </c>
+      <c r="F50" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
-        <v>103</v>
+      <c r="A51" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C51" s="31" t="n">
         <f aca="false">SUM(C77:L77)</f>
@@ -3728,11 +3741,11 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="11" t="s">
-        <v>104</v>
+      <c r="A52" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" s="31" t="n">
         <f aca="false">L75*(1+$B$28)/($B$27-$B$28)</f>
@@ -3752,11 +3765,11 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="11" t="s">
-        <v>105</v>
+      <c r="A53" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C53" s="31" t="n">
         <f aca="false">C52*L76</f>
@@ -3776,11 +3789,11 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="11" t="s">
-        <v>106</v>
+      <c r="A54" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C54" s="31" t="n">
         <f aca="false">C51+C53</f>
@@ -3800,11 +3813,11 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11" t="s">
-        <v>107</v>
+      <c r="A55" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C55" s="31" t="n">
         <f aca="false">$B$8</f>
@@ -3824,11 +3837,11 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11" t="s">
-        <v>108</v>
+      <c r="A56" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C56" s="31" t="n">
         <f aca="false">-$B$9</f>
@@ -3848,11 +3861,11 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11" t="s">
-        <v>109</v>
+      <c r="A57" s="12" t="s">
+        <v>110</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C57" s="31" t="n">
         <f aca="false">C54+C55+C56</f>
@@ -3872,11 +3885,11 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15" t="s">
-        <v>110</v>
+      <c r="A58" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C58" s="34" t="n">
         <f aca="false">C57/$B$7</f>
@@ -3896,11 +3909,11 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="C59" s="35" t="n">
         <f aca="false">$B$5</f>
@@ -3920,11 +3933,11 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15" t="s">
-        <v>113</v>
+      <c r="A60" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C60" s="36" t="n">
         <f aca="false">C58/C59-1</f>
@@ -3944,11 +3957,11 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="11" t="s">
-        <v>114</v>
+      <c r="A61" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C61" s="26" t="n">
         <f aca="false">C53/C54</f>
@@ -3968,11 +3981,11 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="11" t="s">
-        <v>115</v>
+      <c r="A62" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C62" s="26" t="n">
         <f aca="false">1-L73</f>
@@ -3992,11 +4005,11 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="11" t="s">
-        <v>116</v>
+      <c r="A63" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C63" s="26" t="n">
         <f aca="false">IF(C62&gt;0,$B$28/C62,0)</f>
@@ -4016,11 +4029,11 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="11" t="s">
-        <v>117</v>
+      <c r="A64" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C64" s="26" t="n">
         <f aca="false">(G68/$B$10)^(1/5)-1</f>
@@ -4040,24 +4053,24 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
+      <c r="A65" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="9" t="s">
-        <v>119</v>
+      <c r="A66" s="10" t="s">
+        <v>120</v>
       </c>
       <c r="B66" s="37"/>
       <c r="C66" s="37"/>
@@ -4072,8 +4085,8 @@
       <c r="L66" s="37"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15" t="s">
-        <v>120</v>
+      <c r="A67" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C67" s="38" t="n">
         <v>1</v>
@@ -4107,8 +4120,8 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="11" t="s">
-        <v>121</v>
+      <c r="A68" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="C68" s="31" t="n">
         <f aca="false">C$38</f>
@@ -4152,8 +4165,8 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="11" t="s">
-        <v>122</v>
+      <c r="A69" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="C69" s="26" t="n">
         <f aca="false">C68/$B$10-1</f>
@@ -4197,8 +4210,8 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="11" t="s">
-        <v>123</v>
+      <c r="A70" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C70" s="26" t="n">
         <f aca="false">C$43+(C$44-C$43)*MIN(C$67-1,4)/4</f>
@@ -4242,8 +4255,8 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="11" t="s">
-        <v>124</v>
+      <c r="A71" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C71" s="31" t="n">
         <f aca="false">C68*C70</f>
@@ -4287,8 +4300,8 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="11" t="s">
-        <v>125</v>
+      <c r="A72" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C72" s="31" t="n">
         <f aca="false">C71*(1-$B$11)</f>
@@ -4332,8 +4345,8 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="11" t="s">
-        <v>126</v>
+      <c r="A73" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C73" s="26" t="n">
         <f aca="false">C$45+(C$46-C$45)*MIN(C$67-1,4)/4</f>
@@ -4377,8 +4390,8 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="11" t="s">
-        <v>127</v>
+      <c r="A74" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C74" s="31" t="n">
         <f aca="false">C72*(1-C73)</f>
@@ -4422,8 +4435,8 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="15" t="s">
-        <v>128</v>
+      <c r="A75" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C75" s="39" t="n">
         <f aca="false">C72-C74</f>
@@ -4467,8 +4480,8 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="11" t="s">
-        <v>129</v>
+      <c r="A76" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C76" s="40" t="n">
         <f aca="false">1/(1+$B$27)^C$67</f>
@@ -4512,8 +4525,8 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="11" t="s">
-        <v>130</v>
+      <c r="A77" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="C77" s="31" t="n">
         <f aca="false">C75*C76</f>
@@ -4557,8 +4570,8 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="9" t="s">
-        <v>131</v>
+      <c r="A80" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="B80" s="37"/>
       <c r="C80" s="37"/>
@@ -4573,8 +4586,8 @@
       <c r="L80" s="37"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="15" t="s">
-        <v>120</v>
+      <c r="A81" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C81" s="38" t="n">
         <v>1</v>
@@ -4608,8 +4621,8 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="11" t="s">
-        <v>121</v>
+      <c r="A82" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="C82" s="31" t="n">
         <f aca="false">D$38</f>
@@ -4653,8 +4666,8 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="11" t="s">
-        <v>122</v>
+      <c r="A83" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="C83" s="26" t="n">
         <f aca="false">C82/$B$10-1</f>
@@ -4698,8 +4711,8 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="11" t="s">
-        <v>123</v>
+      <c r="A84" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C84" s="26" t="n">
         <f aca="false">D$43+(D$44-D$43)*MIN(C$81-1,4)/4</f>
@@ -4743,8 +4756,8 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="11" t="s">
-        <v>124</v>
+      <c r="A85" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C85" s="31" t="n">
         <f aca="false">C82*C84</f>
@@ -4788,8 +4801,8 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="11" t="s">
-        <v>125</v>
+      <c r="A86" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C86" s="31" t="n">
         <f aca="false">C85*(1-$B$11)</f>
@@ -4833,8 +4846,8 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="11" t="s">
-        <v>126</v>
+      <c r="A87" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C87" s="26" t="n">
         <f aca="false">D$45+(D$46-D$45)*MIN(C$81-1,4)/4</f>
@@ -4878,8 +4891,8 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="11" t="s">
-        <v>127</v>
+      <c r="A88" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C88" s="31" t="n">
         <f aca="false">C86*(1-C87)</f>
@@ -4923,8 +4936,8 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="15" t="s">
-        <v>128</v>
+      <c r="A89" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C89" s="39" t="n">
         <f aca="false">C86-C88</f>
@@ -4968,8 +4981,8 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="11" t="s">
-        <v>129</v>
+      <c r="A90" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C90" s="40" t="n">
         <f aca="false">1/(1+$B$27)^C$81</f>
@@ -5013,8 +5026,8 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="11" t="s">
-        <v>130</v>
+      <c r="A91" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="C91" s="31" t="n">
         <f aca="false">C89*C90</f>
@@ -5058,8 +5071,8 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="9" t="s">
-        <v>132</v>
+      <c r="A94" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="B94" s="37"/>
       <c r="C94" s="37"/>
@@ -5074,8 +5087,8 @@
       <c r="L94" s="37"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="15" t="s">
-        <v>120</v>
+      <c r="A95" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C95" s="38" t="n">
         <v>1</v>
@@ -5109,8 +5122,8 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="11" t="s">
-        <v>121</v>
+      <c r="A96" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="C96" s="31" t="n">
         <f aca="false">E$38</f>
@@ -5154,8 +5167,8 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="11" t="s">
-        <v>122</v>
+      <c r="A97" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="C97" s="26" t="n">
         <f aca="false">C96/$B$10-1</f>
@@ -5199,8 +5212,8 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="11" t="s">
-        <v>123</v>
+      <c r="A98" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C98" s="26" t="n">
         <f aca="false">E$43+(E$44-E$43)*MIN(C$95-1,4)/4</f>
@@ -5244,8 +5257,8 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="11" t="s">
-        <v>124</v>
+      <c r="A99" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C99" s="31" t="n">
         <f aca="false">C96*C98</f>
@@ -5289,8 +5302,8 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="11" t="s">
-        <v>125</v>
+      <c r="A100" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C100" s="31" t="n">
         <f aca="false">C99*(1-$B$11)</f>
@@ -5334,8 +5347,8 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="11" t="s">
-        <v>126</v>
+      <c r="A101" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C101" s="26" t="n">
         <f aca="false">E$45+(E$46-E$45)*MIN(C$95-1,4)/4</f>
@@ -5379,8 +5392,8 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="11" t="s">
-        <v>127</v>
+      <c r="A102" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C102" s="31" t="n">
         <f aca="false">C100*(1-C101)</f>
@@ -5424,8 +5437,8 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="15" t="s">
-        <v>128</v>
+      <c r="A103" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C103" s="39" t="n">
         <f aca="false">C100-C102</f>
@@ -5469,8 +5482,8 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="11" t="s">
-        <v>129</v>
+      <c r="A104" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C104" s="40" t="n">
         <f aca="false">1/(1+$B$27)^C$95</f>
@@ -5514,8 +5527,8 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="11" t="s">
-        <v>130</v>
+      <c r="A105" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="C105" s="31" t="n">
         <f aca="false">C103*C104</f>
@@ -5559,8 +5572,8 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="9" t="s">
-        <v>133</v>
+      <c r="A108" s="10" t="s">
+        <v>134</v>
       </c>
       <c r="B108" s="37"/>
       <c r="C108" s="37"/>
@@ -5575,8 +5588,8 @@
       <c r="L108" s="37"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="15" t="s">
-        <v>120</v>
+      <c r="A109" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C109" s="38" t="n">
         <v>1</v>
@@ -5610,8 +5623,8 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="11" t="s">
-        <v>121</v>
+      <c r="A110" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="C110" s="31" t="n">
         <f aca="false">F$38</f>
@@ -5655,8 +5668,8 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="11" t="s">
-        <v>122</v>
+      <c r="A111" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="C111" s="26" t="n">
         <f aca="false">C110/$B$10-1</f>
@@ -5700,8 +5713,8 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="11" t="s">
-        <v>123</v>
+      <c r="A112" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C112" s="26" t="n">
         <f aca="false">F$43+(F$44-F$43)*MIN(C$109-1,4)/4</f>
@@ -5745,8 +5758,8 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="11" t="s">
-        <v>124</v>
+      <c r="A113" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C113" s="31" t="n">
         <f aca="false">C110*C112</f>
@@ -5790,8 +5803,8 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="11" t="s">
-        <v>125</v>
+      <c r="A114" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C114" s="31" t="n">
         <f aca="false">C113*(1-$B$11)</f>
@@ -5835,8 +5848,8 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="11" t="s">
-        <v>126</v>
+      <c r="A115" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C115" s="26" t="n">
         <f aca="false">F$45+(F$46-F$45)*MIN(C$109-1,4)/4</f>
@@ -5880,8 +5893,8 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="11" t="s">
-        <v>127</v>
+      <c r="A116" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C116" s="31" t="n">
         <f aca="false">C114*(1-C115)</f>
@@ -5925,8 +5938,8 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="15" t="s">
-        <v>128</v>
+      <c r="A117" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C117" s="39" t="n">
         <f aca="false">C114-C116</f>
@@ -5970,8 +5983,8 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="11" t="s">
-        <v>129</v>
+      <c r="A118" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C118" s="40" t="n">
         <f aca="false">1/(1+$B$27)^C$109</f>
@@ -6015,8 +6028,8 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="11" t="s">
-        <v>130</v>
+      <c r="A119" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="C119" s="31" t="n">
         <f aca="false">C117*C118</f>
@@ -6060,32 +6073,32 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
-      <c r="G123" s="8"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="8"/>
-      <c r="J123" s="8"/>
-      <c r="K123" s="8"/>
-      <c r="L123" s="8"/>
+      <c r="A123" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="9"/>
+      <c r="H123" s="9"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="9"/>
+      <c r="K123" s="9"/>
+      <c r="L123" s="9"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="11" t="s">
-        <v>135</v>
+      <c r="A124" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="B124" s="22" t="n">
         <v>0.0075</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="9" t="s">
-        <v>136</v>
+      <c r="A125" s="10" t="s">
+        <v>137</v>
       </c>
       <c r="B125" s="41"/>
       <c r="C125" s="42" t="n">
@@ -6236,7 +6249,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -6271,173 +6284,173 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>140</v>
+      <c r="A4" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G4" s="45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H4" s="45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I4" s="45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J4" s="45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K4" s="45" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L4" s="45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M4" s="45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N4" s="45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O4" s="45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P4" s="45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q4" s="45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G5" s="46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I5" s="46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J5" s="46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K5" s="46" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M5" s="46" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O5" s="46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P5" s="46" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q5" s="46" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L6" s="46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M6" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O6" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P6" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q6" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M7" s="47" t="n">
         <v>1</v>
@@ -6456,8 +6469,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>178</v>
+      <c r="A8" s="7" t="s">
+        <v>179</v>
       </c>
       <c r="B8" s="48" t="n">
         <v>6910</v>
@@ -6514,8 +6527,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>179</v>
+      <c r="A9" s="12" t="s">
+        <v>180</v>
       </c>
       <c r="C9" s="26" t="n">
         <f aca="false">C8/B8-1</f>
@@ -6575,8 +6588,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>180</v>
+      <c r="A10" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="B10" s="48" t="n">
         <v>2847</v>
@@ -6630,8 +6643,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>181</v>
+      <c r="A11" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="B11" s="51" t="n">
         <f aca="false">B8-B10</f>
@@ -6698,8 +6711,8 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>182</v>
+      <c r="A12" s="12" t="s">
+        <v>183</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">B11/B8</f>
@@ -6767,8 +6780,8 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>183</v>
+      <c r="A13" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="B13" s="48" t="n">
         <v>1466</v>
@@ -6822,8 +6835,8 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>184</v>
+      <c r="A14" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="B14" s="48" t="n">
         <v>663</v>
@@ -6877,8 +6890,8 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>185</v>
+      <c r="A15" s="12" t="s">
+        <v>186</v>
       </c>
       <c r="B15" s="48" t="n">
         <v>0</v>
@@ -6927,8 +6940,8 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>186</v>
+      <c r="A16" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="B16" s="50" t="n">
         <f aca="false">SUM(B13:B15)</f>
@@ -6992,8 +7005,8 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>187</v>
+      <c r="A17" s="7" t="s">
+        <v>188</v>
       </c>
       <c r="B17" s="51" t="n">
         <f aca="false">B11-B16</f>
@@ -7060,8 +7073,8 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
-        <v>188</v>
+      <c r="A18" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="B18" s="26" t="n">
         <f aca="false">B17/B8</f>
@@ -7107,30 +7120,30 @@
         <f aca="false">L17/L8</f>
         <v>0.652140475954715</v>
       </c>
-      <c r="M18" s="14" t="n">
+      <c r="M18" s="15" t="n">
         <f aca="false">NVDA!C84</f>
         <v>0.62</v>
       </c>
-      <c r="N18" s="14" t="n">
+      <c r="N18" s="15" t="n">
         <f aca="false">NVDA!D84</f>
         <v>0.6025</v>
       </c>
-      <c r="O18" s="14" t="n">
+      <c r="O18" s="15" t="n">
         <f aca="false">NVDA!E84</f>
         <v>0.585</v>
       </c>
-      <c r="P18" s="14" t="n">
+      <c r="P18" s="15" t="n">
         <f aca="false">NVDA!F84</f>
         <v>0.5675</v>
       </c>
-      <c r="Q18" s="14" t="n">
+      <c r="Q18" s="15" t="n">
         <f aca="false">NVDA!G84</f>
         <v>0.55</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>189</v>
+      <c r="A19" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="B19" s="48" t="n">
         <v>-29</v>
@@ -7184,8 +7197,8 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>190</v>
+      <c r="A20" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="B20" s="50" t="n">
         <f aca="false">B17+B19</f>
@@ -7249,8 +7262,8 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>191</v>
+      <c r="A21" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="B21" s="48" t="n">
         <v>239</v>
@@ -7304,8 +7317,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>192</v>
+      <c r="A22" s="12" t="s">
+        <v>193</v>
       </c>
       <c r="B22" s="26" t="n">
         <f aca="false">B21/B20</f>
@@ -7369,8 +7382,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>193</v>
+      <c r="A23" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="B23" s="51" t="n">
         <f aca="false">B20-B21</f>
@@ -7437,8 +7450,8 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>194</v>
+      <c r="A24" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="B24" s="26" t="n">
         <f aca="false">B23/B8</f>
@@ -7506,8 +7519,8 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>195</v>
+      <c r="A25" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="B25" s="48" t="n">
         <v>25960</v>
@@ -7561,8 +7574,8 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>196</v>
+      <c r="A26" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="B26" s="34" t="n">
         <f aca="false">B23/B25</f>
@@ -7629,8 +7642,8 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>197</v>
+      <c r="A27" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="C27" s="26" t="n">
         <f aca="false">C26/B26-1</f>
@@ -7690,8 +7703,8 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
-        <v>198</v>
+      <c r="A28" s="12" t="s">
+        <v>199</v>
       </c>
       <c r="B28" s="48" t="n">
         <v>1496</v>
@@ -7748,8 +7761,8 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>199</v>
+      <c r="A29" s="12" t="s">
+        <v>200</v>
       </c>
       <c r="B29" s="26" t="n">
         <f aca="false">B28/B8</f>
@@ -7817,8 +7830,8 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="s">
-        <v>200</v>
+      <c r="A30" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="B30" s="48" t="n">
         <v>176</v>
@@ -7852,8 +7865,8 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
-        <v>201</v>
+      <c r="A31" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="B31" s="26" t="n">
         <f aca="false">B30/B8</f>
@@ -7897,29 +7910,29 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
+      <c r="A33" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>203</v>
+      <c r="A34" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="B34" s="48" t="n">
         <v>1934</v>
@@ -7953,8 +7966,8 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
-        <v>204</v>
+      <c r="A35" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="B35" s="50" t="n">
         <f aca="false">B17-B34</f>
@@ -7998,8 +8011,8 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
-        <v>205</v>
+      <c r="A36" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="B36" s="48" t="n">
         <v>1666</v>
@@ -8033,8 +8046,8 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="s">
-        <v>204</v>
+      <c r="A37" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="B37" s="50" t="n">
         <f aca="false">B23-B36</f>
@@ -8078,99 +8091,99 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
-      <c r="Q39" s="8"/>
+      <c r="A39" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
-        <v>207</v>
+      <c r="A40" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="B40" s="52" t="n">
         <v>0.73</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
-        <v>208</v>
+      <c r="A41" s="12" t="s">
+        <v>209</v>
       </c>
       <c r="B41" s="52" t="n">
         <v>0.69</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
-        <v>209</v>
+      <c r="A42" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="B42" s="21" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11" t="s">
-        <v>210</v>
+      <c r="A43" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="B43" s="22" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>211</v>
+      <c r="A44" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="B44" s="21" t="n">
         <v>-0.005</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="B45" s="14" t="n">
+      <c r="A45" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B45" s="15" t="n">
         <f aca="false">NVDA!B11</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
+      <c r="A48" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11" t="s">
-        <v>214</v>
+      <c r="A49" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="B49" s="26" t="n">
         <f aca="false">(K8/H8)^(1/3)-1</f>
@@ -8178,8 +8191,8 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="11" t="s">
-        <v>46</v>
+      <c r="A50" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="B50" s="26" t="n">
         <f aca="false">(K8/F8)^(1/5)-1</f>
@@ -8187,8 +8200,8 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
-        <v>215</v>
+      <c r="A51" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="B51" s="26" t="n">
         <f aca="false">(K8/B8)^(1/9)-1</f>
@@ -8196,8 +8209,8 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="11" t="s">
-        <v>216</v>
+      <c r="A52" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="B52" s="26" t="n">
         <f aca="false">(Q8/L8)^(1/5)-1</f>
@@ -8205,8 +8218,8 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="11" t="s">
-        <v>217</v>
+      <c r="A53" s="12" t="s">
+        <v>218</v>
       </c>
       <c r="B53" s="26" t="n">
         <f aca="false">AVERAGE(B18:K18)</f>
@@ -8214,8 +8227,8 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="11" t="s">
-        <v>218</v>
+      <c r="A54" s="12" t="s">
+        <v>219</v>
       </c>
       <c r="B54" s="26" t="n">
         <f aca="false">K18</f>
@@ -8223,8 +8236,8 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11" t="s">
-        <v>219</v>
+      <c r="A55" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="B55" s="26" t="n">
         <f aca="false">Q18</f>
@@ -8232,8 +8245,8 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11" t="s">
-        <v>220</v>
+      <c r="A56" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="B56" s="26" t="n">
         <f aca="false">(K26/B26)^(1/9)-1</f>
@@ -8241,8 +8254,8 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11" t="s">
-        <v>221</v>
+      <c r="A57" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="B57" s="26" t="n">
         <f aca="false">(Q26/L26)^(1/5)-1</f>
@@ -8251,7 +8264,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -8281,49 +8294,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="A4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>28</v>
+      <c r="A5" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>665.75</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>51</v>
+      <c r="A6" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="B6" s="19" t="n">
         <v>1700</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>52</v>
+      <c r="A7" s="12" t="s">
+        <v>53</v>
       </c>
       <c r="B7" s="20" t="n">
         <f aca="false">B6/B5</f>
@@ -8331,88 +8344,88 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>53</v>
+      <c r="A8" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="B8" s="19" t="n">
         <v>90.26</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>54</v>
+      <c r="A9" s="12" t="s">
+        <v>55</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>112.32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>55</v>
+      <c r="A10" s="12" t="s">
+        <v>56</v>
       </c>
       <c r="B10" s="19" t="n">
         <v>228.25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>56</v>
+      <c r="A11" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="B11" s="21" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
+      <c r="A13" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>58</v>
+      <c r="A14" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="B14" s="22" t="n">
         <v>0.0494</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>59</v>
+      <c r="A15" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="B15" s="22" t="n">
         <v>0.045</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>60</v>
+      <c r="A16" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="B16" s="23" t="n">
         <v>1.24</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>61</v>
+      <c r="A17" s="12" t="s">
+        <v>62</v>
       </c>
       <c r="B17" s="23" t="n">
         <v>0.67</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
-        <v>62</v>
+      <c r="A18" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="B18" s="24" t="n">
         <f aca="false">B17*B16+(1-B17)*1</f>
@@ -8420,8 +8433,8 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>63</v>
+      <c r="A19" s="12" t="s">
+        <v>64</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">B14+B18*B15</f>
@@ -8429,16 +8442,16 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>64</v>
+      <c r="A20" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="B20" s="22" t="n">
         <v>0.0575</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>65</v>
+      <c r="A21" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="B21" s="25" t="n">
         <f aca="false">B20*(1-B11)</f>
@@ -8446,8 +8459,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>66</v>
+      <c r="A22" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="B22" s="26" t="n">
         <f aca="false">B6/(B6+B9)</f>
@@ -8455,8 +8468,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
-        <v>67</v>
+      <c r="A23" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="B23" s="26" t="n">
         <f aca="false">B9/(B6+B9)</f>
@@ -8464,8 +8477,8 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>68</v>
+      <c r="A24" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">B22*B19+B23*B21</f>
@@ -8473,24 +8486,24 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>69</v>
+      <c r="A25" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="B25" s="27" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>70</v>
+      <c r="A26" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="B26" s="27" t="n">
         <v>0.11</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>29</v>
+      <c r="A27" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="B27" s="28" t="n">
         <f aca="false">MEDIAN(B25,B24,B26)</f>
@@ -8498,63 +8511,63 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
-        <v>71</v>
+      <c r="A28" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="B28" s="27" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>72</v>
+      <c r="A29" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="B29" s="27" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
+      <c r="A31" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="A32" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="B32" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="C32" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="D32" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="E32" s="11" t="s">
         <v>79</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C33" s="30"/>
       <c r="D33" s="30"/>
@@ -8569,10 +8582,10 @@
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C34" s="30"/>
       <c r="D34" s="30"/>
@@ -8587,10 +8600,10 @@
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C35" s="30"/>
       <c r="D35" s="30"/>
@@ -8605,10 +8618,10 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C36" s="30"/>
       <c r="D36" s="30"/>
@@ -8622,11 +8635,11 @@
       <c r="L36" s="30"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11" t="s">
-        <v>88</v>
+      <c r="A38" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C38" s="19" t="n">
         <v>255</v>
@@ -8643,11 +8656,11 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="11" t="s">
-        <v>90</v>
+      <c r="A39" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" s="21" t="n">
         <v>0.06</v>
@@ -8664,11 +8677,11 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="C40" s="21" t="n">
         <v>0.04</v>
@@ -8685,11 +8698,11 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
-        <v>93</v>
+      <c r="A41" s="12" t="s">
+        <v>94</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C41" s="21" t="n">
         <v>0.03</v>
@@ -8706,11 +8719,11 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
-        <v>94</v>
+      <c r="A42" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C42" s="21" t="n">
         <v>0.03</v>
@@ -8727,11 +8740,11 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11" t="s">
-        <v>95</v>
+      <c r="A43" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C43" s="21" t="n">
         <v>0.3</v>
@@ -8748,11 +8761,11 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>96</v>
+      <c r="A44" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C44" s="21" t="n">
         <v>0.28</v>
@@ -8769,11 +8782,11 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
-        <v>97</v>
+      <c r="A45" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C45" s="21" t="n">
         <v>0.45</v>
@@ -8790,11 +8803,11 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="s">
-        <v>98</v>
+      <c r="A46" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C46" s="21" t="n">
         <v>0.6</v>
@@ -8811,11 +8824,11 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="11" t="s">
-        <v>99</v>
+      <c r="A47" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C47" s="32" t="n">
         <v>1</v>
@@ -8830,51 +8843,51 @@
         <v>1.8223</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
+      <c r="A49" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" s="10" t="s">
+      <c r="A50" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="C50" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="D50" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="E50" s="11" t="s">
         <v>79</v>
       </c>
+      <c r="F50" s="11" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
-        <v>103</v>
+      <c r="A51" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C51" s="31" t="n">
         <f aca="false">SUM(C77:L77)</f>
@@ -8894,11 +8907,11 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="11" t="s">
-        <v>104</v>
+      <c r="A52" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" s="31" t="n">
         <f aca="false">L75*(1+$B$28)/($B$27-$B$28)</f>
@@ -8918,11 +8931,11 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="11" t="s">
-        <v>105</v>
+      <c r="A53" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C53" s="31" t="n">
         <f aca="false">C52*L76</f>
@@ -8942,11 +8955,11 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="11" t="s">
-        <v>106</v>
+      <c r="A54" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C54" s="31" t="n">
         <f aca="false">C51+C53</f>
@@ -8966,11 +8979,11 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11" t="s">
-        <v>107</v>
+      <c r="A55" s="12" t="s">
+        <v>108</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C55" s="31" t="n">
         <f aca="false">$B$8</f>
@@ -8990,11 +9003,11 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11" t="s">
-        <v>108</v>
+      <c r="A56" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C56" s="31" t="n">
         <f aca="false">-$B$9</f>
@@ -9014,11 +9027,11 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11" t="s">
-        <v>109</v>
+      <c r="A57" s="12" t="s">
+        <v>110</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C57" s="31" t="n">
         <f aca="false">C54+C55+C56</f>
@@ -9038,11 +9051,11 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15" t="s">
-        <v>110</v>
+      <c r="A58" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C58" s="34" t="n">
         <f aca="false">C57/$B$7</f>
@@ -9062,11 +9075,11 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="C59" s="35" t="n">
         <f aca="false">$B$5</f>
@@ -9086,11 +9099,11 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="15" t="s">
-        <v>113</v>
+      <c r="A60" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C60" s="36" t="n">
         <f aca="false">C58/C59-1</f>
@@ -9110,11 +9123,11 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="11" t="s">
-        <v>114</v>
+      <c r="A61" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C61" s="26" t="n">
         <f aca="false">C53/C54</f>
@@ -9134,11 +9147,11 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="11" t="s">
-        <v>115</v>
+      <c r="A62" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C62" s="26" t="n">
         <f aca="false">1-L73</f>
@@ -9158,11 +9171,11 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="11" t="s">
-        <v>116</v>
+      <c r="A63" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C63" s="26" t="n">
         <f aca="false">IF(C62&gt;0,$B$28/C62,0)</f>
@@ -9182,11 +9195,11 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="11" t="s">
-        <v>117</v>
+      <c r="A64" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C64" s="26" t="n">
         <f aca="false">(G68/$B$10)^(1/5)-1</f>
@@ -9206,24 +9219,24 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
+      <c r="A65" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="9" t="s">
-        <v>119</v>
+      <c r="A66" s="10" t="s">
+        <v>120</v>
       </c>
       <c r="B66" s="37"/>
       <c r="C66" s="37"/>
@@ -9238,8 +9251,8 @@
       <c r="L66" s="37"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15" t="s">
-        <v>120</v>
+      <c r="A67" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C67" s="38" t="n">
         <v>1</v>
@@ -9273,8 +9286,8 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="11" t="s">
-        <v>121</v>
+      <c r="A68" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="C68" s="31" t="n">
         <f aca="false">C$38</f>
@@ -9318,8 +9331,8 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="11" t="s">
-        <v>122</v>
+      <c r="A69" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="C69" s="26" t="n">
         <f aca="false">C68/$B$10-1</f>
@@ -9363,8 +9376,8 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="11" t="s">
-        <v>123</v>
+      <c r="A70" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C70" s="26" t="n">
         <f aca="false">C$43+(C$44-C$43)*MIN(C$67-1,4)/4</f>
@@ -9408,8 +9421,8 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="11" t="s">
-        <v>124</v>
+      <c r="A71" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C71" s="31" t="n">
         <f aca="false">C68*C70</f>
@@ -9453,8 +9466,8 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="11" t="s">
-        <v>125</v>
+      <c r="A72" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C72" s="31" t="n">
         <f aca="false">C71*(1-$B$11)</f>
@@ -9498,8 +9511,8 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="11" t="s">
-        <v>126</v>
+      <c r="A73" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C73" s="26" t="n">
         <f aca="false">C$45+(C$46-C$45)*MIN(C$67-1,4)/4</f>
@@ -9543,8 +9556,8 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="11" t="s">
-        <v>127</v>
+      <c r="A74" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C74" s="31" t="n">
         <f aca="false">C72*(1-C73)</f>
@@ -9588,8 +9601,8 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="15" t="s">
-        <v>128</v>
+      <c r="A75" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C75" s="39" t="n">
         <f aca="false">C72-C74</f>
@@ -9633,8 +9646,8 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="11" t="s">
-        <v>129</v>
+      <c r="A76" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C76" s="40" t="n">
         <f aca="false">1/(1+$B$27)^C$67</f>
@@ -9678,8 +9691,8 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="11" t="s">
-        <v>130</v>
+      <c r="A77" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="C77" s="31" t="n">
         <f aca="false">C75*C76</f>
@@ -9723,8 +9736,8 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="9" t="s">
-        <v>131</v>
+      <c r="A80" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="B80" s="37"/>
       <c r="C80" s="37"/>
@@ -9739,8 +9752,8 @@
       <c r="L80" s="37"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="15" t="s">
-        <v>120</v>
+      <c r="A81" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C81" s="38" t="n">
         <v>1</v>
@@ -9774,8 +9787,8 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="11" t="s">
-        <v>121</v>
+      <c r="A82" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="C82" s="31" t="n">
         <f aca="false">D$38</f>
@@ -9819,8 +9832,8 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="11" t="s">
-        <v>122</v>
+      <c r="A83" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="C83" s="26" t="n">
         <f aca="false">C82/$B$10-1</f>
@@ -9864,8 +9877,8 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="11" t="s">
-        <v>123</v>
+      <c r="A84" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C84" s="26" t="n">
         <f aca="false">D$43+(D$44-D$43)*MIN(C$81-1,4)/4</f>
@@ -9909,8 +9922,8 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="11" t="s">
-        <v>124</v>
+      <c r="A85" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C85" s="31" t="n">
         <f aca="false">C82*C84</f>
@@ -9954,8 +9967,8 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="11" t="s">
-        <v>125</v>
+      <c r="A86" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C86" s="31" t="n">
         <f aca="false">C85*(1-$B$11)</f>
@@ -9999,8 +10012,8 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="11" t="s">
-        <v>126</v>
+      <c r="A87" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C87" s="26" t="n">
         <f aca="false">D$45+(D$46-D$45)*MIN(C$81-1,4)/4</f>
@@ -10044,8 +10057,8 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="11" t="s">
-        <v>127</v>
+      <c r="A88" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C88" s="31" t="n">
         <f aca="false">C86*(1-C87)</f>
@@ -10089,8 +10102,8 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="15" t="s">
-        <v>128</v>
+      <c r="A89" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C89" s="39" t="n">
         <f aca="false">C86-C88</f>
@@ -10134,8 +10147,8 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="11" t="s">
-        <v>129</v>
+      <c r="A90" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C90" s="40" t="n">
         <f aca="false">1/(1+$B$27)^C$81</f>
@@ -10179,8 +10192,8 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="11" t="s">
-        <v>130</v>
+      <c r="A91" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="C91" s="31" t="n">
         <f aca="false">C89*C90</f>
@@ -10224,8 +10237,8 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="9" t="s">
-        <v>132</v>
+      <c r="A94" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="B94" s="37"/>
       <c r="C94" s="37"/>
@@ -10240,8 +10253,8 @@
       <c r="L94" s="37"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="15" t="s">
-        <v>120</v>
+      <c r="A95" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C95" s="38" t="n">
         <v>1</v>
@@ -10275,8 +10288,8 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="11" t="s">
-        <v>121</v>
+      <c r="A96" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="C96" s="31" t="n">
         <f aca="false">E$38</f>
@@ -10320,8 +10333,8 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="11" t="s">
-        <v>122</v>
+      <c r="A97" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="C97" s="26" t="n">
         <f aca="false">C96/$B$10-1</f>
@@ -10365,8 +10378,8 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="11" t="s">
-        <v>123</v>
+      <c r="A98" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C98" s="26" t="n">
         <f aca="false">E$43+(E$44-E$43)*MIN(C$95-1,4)/4</f>
@@ -10410,8 +10423,8 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="11" t="s">
-        <v>124</v>
+      <c r="A99" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C99" s="31" t="n">
         <f aca="false">C96*C98</f>
@@ -10455,8 +10468,8 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="11" t="s">
-        <v>125</v>
+      <c r="A100" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C100" s="31" t="n">
         <f aca="false">C99*(1-$B$11)</f>
@@ -10500,8 +10513,8 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="11" t="s">
-        <v>126</v>
+      <c r="A101" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C101" s="26" t="n">
         <f aca="false">E$45+(E$46-E$45)*MIN(C$95-1,4)/4</f>
@@ -10545,8 +10558,8 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="11" t="s">
-        <v>127</v>
+      <c r="A102" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C102" s="31" t="n">
         <f aca="false">C100*(1-C101)</f>
@@ -10590,8 +10603,8 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="15" t="s">
-        <v>128</v>
+      <c r="A103" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C103" s="39" t="n">
         <f aca="false">C100-C102</f>
@@ -10635,8 +10648,8 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="11" t="s">
-        <v>129</v>
+      <c r="A104" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C104" s="40" t="n">
         <f aca="false">1/(1+$B$27)^C$95</f>
@@ -10680,8 +10693,8 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="11" t="s">
-        <v>130</v>
+      <c r="A105" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="C105" s="31" t="n">
         <f aca="false">C103*C104</f>
@@ -10725,8 +10738,8 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="9" t="s">
-        <v>133</v>
+      <c r="A108" s="10" t="s">
+        <v>134</v>
       </c>
       <c r="B108" s="37"/>
       <c r="C108" s="37"/>
@@ -10741,8 +10754,8 @@
       <c r="L108" s="37"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="15" t="s">
-        <v>120</v>
+      <c r="A109" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="C109" s="38" t="n">
         <v>1</v>
@@ -10776,8 +10789,8 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="11" t="s">
-        <v>121</v>
+      <c r="A110" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="C110" s="31" t="n">
         <f aca="false">F$38</f>
@@ -10821,8 +10834,8 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="11" t="s">
-        <v>122</v>
+      <c r="A111" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="C111" s="26" t="n">
         <f aca="false">C110/$B$10-1</f>
@@ -10866,8 +10879,8 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="11" t="s">
-        <v>123</v>
+      <c r="A112" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C112" s="26" t="n">
         <f aca="false">F$43+(F$44-F$43)*MIN(C$109-1,4)/4</f>
@@ -10911,8 +10924,8 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="11" t="s">
-        <v>124</v>
+      <c r="A113" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C113" s="31" t="n">
         <f aca="false">C110*C112</f>
@@ -10956,8 +10969,8 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="11" t="s">
-        <v>125</v>
+      <c r="A114" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C114" s="31" t="n">
         <f aca="false">C113*(1-$B$11)</f>
@@ -11001,8 +11014,8 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="11" t="s">
-        <v>126</v>
+      <c r="A115" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C115" s="26" t="n">
         <f aca="false">F$45+(F$46-F$45)*MIN(C$109-1,4)/4</f>
@@ -11046,8 +11059,8 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="11" t="s">
-        <v>127</v>
+      <c r="A116" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C116" s="31" t="n">
         <f aca="false">C114*(1-C115)</f>
@@ -11091,8 +11104,8 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="15" t="s">
-        <v>128</v>
+      <c r="A117" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C117" s="39" t="n">
         <f aca="false">C114-C116</f>
@@ -11136,8 +11149,8 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="11" t="s">
-        <v>129</v>
+      <c r="A118" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C118" s="40" t="n">
         <f aca="false">1/(1+$B$27)^C$109</f>
@@ -11181,8 +11194,8 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="11" t="s">
-        <v>130</v>
+      <c r="A119" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="C119" s="31" t="n">
         <f aca="false">C117*C118</f>
@@ -11226,32 +11239,32 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="8"/>
-      <c r="G123" s="8"/>
-      <c r="H123" s="8"/>
-      <c r="I123" s="8"/>
-      <c r="J123" s="8"/>
-      <c r="K123" s="8"/>
-      <c r="L123" s="8"/>
+      <c r="A123" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B123" s="9"/>
+      <c r="C123" s="9"/>
+      <c r="D123" s="9"/>
+      <c r="E123" s="9"/>
+      <c r="F123" s="9"/>
+      <c r="G123" s="9"/>
+      <c r="H123" s="9"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="9"/>
+      <c r="K123" s="9"/>
+      <c r="L123" s="9"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="11" t="s">
-        <v>135</v>
+      <c r="A124" s="12" t="s">
+        <v>136</v>
       </c>
       <c r="B124" s="22" t="n">
         <v>0.0075</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="9" t="s">
-        <v>136</v>
+      <c r="A125" s="10" t="s">
+        <v>137</v>
       </c>
       <c r="B125" s="41"/>
       <c r="C125" s="42" t="n">
@@ -11402,7 +11415,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -11437,173 +11450,173 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>140</v>
+      <c r="A4" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G4" s="45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H4" s="45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I4" s="45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J4" s="45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K4" s="45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L4" s="45" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M4" s="45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N4" s="45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O4" s="45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P4" s="45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q4" s="45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G5" s="46" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I5" s="46" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J5" s="46" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K5" s="46" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M5" s="46" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N5" s="46" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O5" s="46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P5" s="46" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q5" s="46" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K6" s="46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L6" s="46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M6" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N6" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O6" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P6" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q6" s="46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M7" s="47" t="n">
         <v>1</v>
@@ -11622,8 +11635,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
-        <v>178</v>
+      <c r="A8" s="7" t="s">
+        <v>179</v>
       </c>
       <c r="B8" s="48" t="n">
         <v>27638</v>
@@ -11680,8 +11693,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>179</v>
+      <c r="A9" s="12" t="s">
+        <v>180</v>
       </c>
       <c r="C9" s="26" t="n">
         <f aca="false">C8/B8-1</f>
@@ -11741,8 +11754,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>180</v>
+      <c r="A10" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="B10" s="48" t="n">
         <v>3789</v>
@@ -11796,8 +11809,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>181</v>
+      <c r="A11" s="7" t="s">
+        <v>182</v>
       </c>
       <c r="B11" s="51" t="n">
         <f aca="false">B8-B10</f>
@@ -11864,8 +11877,8 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>182</v>
+      <c r="A12" s="12" t="s">
+        <v>183</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">B11/B8</f>
@@ -11933,8 +11946,8 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>183</v>
+      <c r="A13" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="B13" s="48" t="n">
         <v>5919</v>
@@ -11988,8 +12001,8 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>184</v>
+      <c r="A14" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="B14" s="48" t="n">
         <f aca="false">3772+1731</f>
@@ -12053,8 +12066,8 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
-        <v>185</v>
+      <c r="A15" s="12" t="s">
+        <v>186</v>
       </c>
       <c r="B15" s="48" t="n">
         <v>0</v>
@@ -12103,8 +12116,8 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>186</v>
+      <c r="A16" s="12" t="s">
+        <v>187</v>
       </c>
       <c r="B16" s="50" t="n">
         <f aca="false">SUM(B13:B15)</f>
@@ -12168,8 +12181,8 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
-        <v>187</v>
+      <c r="A17" s="7" t="s">
+        <v>188</v>
       </c>
       <c r="B17" s="51" t="n">
         <f aca="false">B11-B16</f>
@@ -12236,8 +12249,8 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
-        <v>188</v>
+      <c r="A18" s="12" t="s">
+        <v>189</v>
       </c>
       <c r="B18" s="26" t="n">
         <f aca="false">B17/B8</f>
@@ -12283,30 +12296,30 @@
         <f aca="false">L17/L8</f>
         <v>0.380841807340294</v>
       </c>
-      <c r="M18" s="14" t="n">
+      <c r="M18" s="15" t="n">
         <f aca="false">META!C84</f>
         <v>0.34</v>
       </c>
-      <c r="N18" s="14" t="n">
+      <c r="N18" s="15" t="n">
         <f aca="false">META!D84</f>
         <v>0.345</v>
       </c>
-      <c r="O18" s="14" t="n">
+      <c r="O18" s="15" t="n">
         <f aca="false">META!E84</f>
         <v>0.35</v>
       </c>
-      <c r="P18" s="14" t="n">
+      <c r="P18" s="15" t="n">
         <f aca="false">META!F84</f>
         <v>0.355</v>
       </c>
-      <c r="Q18" s="14" t="n">
+      <c r="Q18" s="15" t="n">
         <f aca="false">META!G84</f>
         <v>0.36</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>189</v>
+      <c r="A19" s="12" t="s">
+        <v>190</v>
       </c>
       <c r="B19" s="48" t="n">
         <v>91</v>
@@ -12360,8 +12373,8 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>190</v>
+      <c r="A20" s="12" t="s">
+        <v>191</v>
       </c>
       <c r="B20" s="50" t="n">
         <f aca="false">B17+B19</f>
@@ -12425,8 +12438,8 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>191</v>
+      <c r="A21" s="12" t="s">
+        <v>192</v>
       </c>
       <c r="B21" s="48" t="n">
         <v>2301</v>
@@ -12480,8 +12493,8 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>192</v>
+      <c r="A22" s="12" t="s">
+        <v>193</v>
       </c>
       <c r="B22" s="26" t="n">
         <f aca="false">B21/B20</f>
@@ -12545,8 +12558,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
-        <v>193</v>
+      <c r="A23" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="B23" s="51" t="n">
         <f aca="false">B20-B21</f>
@@ -12613,8 +12626,8 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>194</v>
+      <c r="A24" s="12" t="s">
+        <v>195</v>
       </c>
       <c r="B24" s="26" t="n">
         <f aca="false">B23/B8</f>
@@ -12682,8 +12695,8 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>195</v>
+      <c r="A25" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="B25" s="48" t="n">
         <v>2925</v>
@@ -12737,8 +12750,8 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
-        <v>196</v>
+      <c r="A26" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="B26" s="34" t="n">
         <f aca="false">B23/B25</f>
@@ -12805,8 +12818,8 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>197</v>
+      <c r="A27" s="12" t="s">
+        <v>198</v>
       </c>
       <c r="C27" s="26" t="n">
         <f aca="false">C26/B26-1</f>
@@ -12866,8 +12879,8 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
-        <v>198</v>
+      <c r="A28" s="12" t="s">
+        <v>199</v>
       </c>
       <c r="B28" s="48" t="n">
         <v>11617</v>
@@ -12924,8 +12937,8 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>199</v>
+      <c r="A29" s="12" t="s">
+        <v>200</v>
       </c>
       <c r="B29" s="26" t="n">
         <f aca="false">B28/B8</f>
@@ -12993,8 +13006,8 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="s">
-        <v>200</v>
+      <c r="A30" s="12" t="s">
+        <v>201</v>
       </c>
       <c r="B30" s="48" t="n">
         <v>4491</v>
@@ -13028,8 +13041,8 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
-        <v>201</v>
+      <c r="A31" s="12" t="s">
+        <v>202</v>
       </c>
       <c r="B31" s="26" t="n">
         <f aca="false">B30/B8</f>
@@ -13073,29 +13086,29 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
+      <c r="A33" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>203</v>
+      <c r="A34" s="12" t="s">
+        <v>204</v>
       </c>
       <c r="B34" s="48" t="n">
         <v>12427</v>
@@ -13129,8 +13142,8 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
-        <v>204</v>
+      <c r="A35" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="B35" s="50" t="n">
         <f aca="false">B17-B34</f>
@@ -13174,8 +13187,8 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
-        <v>205</v>
+      <c r="A36" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="B36" s="48" t="n">
         <v>10217</v>
@@ -13209,8 +13222,8 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="s">
-        <v>204</v>
+      <c r="A37" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="B37" s="50" t="n">
         <f aca="false">B23-B36</f>
@@ -13254,99 +13267,99 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="8"/>
-      <c r="N39" s="8"/>
-      <c r="O39" s="8"/>
-      <c r="P39" s="8"/>
-      <c r="Q39" s="8"/>
+      <c r="A39" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
-        <v>207</v>
+      <c r="A40" s="12" t="s">
+        <v>208</v>
       </c>
       <c r="B40" s="52" t="n">
         <v>0.78</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
-        <v>208</v>
+      <c r="A41" s="12" t="s">
+        <v>209</v>
       </c>
       <c r="B41" s="52" t="n">
         <v>0.77</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
-        <v>209</v>
+      <c r="A42" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="B42" s="21" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11" t="s">
-        <v>210</v>
+      <c r="A43" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="B43" s="22" t="n">
         <v>0.008</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>211</v>
+      <c r="A44" s="12" t="s">
+        <v>212</v>
       </c>
       <c r="B44" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="B45" s="14" t="n">
+      <c r="A45" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="B45" s="15" t="n">
         <f aca="false">META!B11</f>
         <v>0.15</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="8"/>
+      <c r="A48" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="11" t="s">
-        <v>214</v>
+      <c r="A49" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="B49" s="26" t="n">
         <f aca="false">(K8/H8)^(1/3)-1</f>
@@ -13354,8 +13367,8 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="11" t="s">
-        <v>46</v>
+      <c r="A50" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="B50" s="26" t="n">
         <f aca="false">(K8/F8)^(1/5)-1</f>
@@ -13363,8 +13376,8 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="11" t="s">
-        <v>215</v>
+      <c r="A51" s="12" t="s">
+        <v>216</v>
       </c>
       <c r="B51" s="26" t="n">
         <f aca="false">(K8/B8)^(1/9)-1</f>
@@ -13372,8 +13385,8 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="11" t="s">
-        <v>216</v>
+      <c r="A52" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="B52" s="26" t="n">
         <f aca="false">(Q8/L8)^(1/5)-1</f>
@@ -13381,8 +13394,8 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="11" t="s">
-        <v>217</v>
+      <c r="A53" s="12" t="s">
+        <v>218</v>
       </c>
       <c r="B53" s="26" t="n">
         <f aca="false">AVERAGE(B18:K18)</f>
@@ -13390,8 +13403,8 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="11" t="s">
-        <v>218</v>
+      <c r="A54" s="12" t="s">
+        <v>219</v>
       </c>
       <c r="B54" s="26" t="n">
         <f aca="false">K18</f>
@@ -13399,8 +13412,8 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="11" t="s">
-        <v>219</v>
+      <c r="A55" s="12" t="s">
+        <v>220</v>
       </c>
       <c r="B55" s="26" t="n">
         <f aca="false">Q18</f>
@@ -13408,8 +13421,8 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="11" t="s">
-        <v>220</v>
+      <c r="A56" s="12" t="s">
+        <v>221</v>
       </c>
       <c r="B56" s="26" t="n">
         <f aca="false">(K26/B26)^(1/9)-1</f>
@@ -13417,8 +13430,8 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11" t="s">
-        <v>221</v>
+      <c r="A57" s="12" t="s">
+        <v>222</v>
       </c>
       <c r="B57" s="26" t="n">
         <f aca="false">(Q26/L26)^(1/5)-1</f>
@@ -13427,7 +13440,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -13457,71 +13470,71 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
+      <c r="A4" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>244</v>
+      <c r="C5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="12" t="n">
+      <c r="A6" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="13" t="n">
         <f aca="false">NVDA!B5</f>
         <v>222.27</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="13" t="n">
         <f aca="false">META!B5</f>
         <v>665.75</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B7" s="12" t="n">
+      <c r="A7" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" s="13" t="n">
         <f aca="false">NVDA_PnL!L26</f>
         <v>7.91</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="13" t="n">
         <f aca="false">META_PnL!L26</f>
         <v>26.54</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>248</v>
+      <c r="A8" s="12" t="s">
+        <v>249</v>
       </c>
       <c r="B8" s="32" t="n">
         <f aca="false">B6/B7</f>
@@ -13532,12 +13545,12 @@
         <v>25.0847776940467</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>250</v>
+      <c r="A9" s="12" t="s">
+        <v>251</v>
       </c>
       <c r="B9" s="53" t="n">
         <v>28.11</v>
@@ -13546,12 +13559,12 @@
         <v>25.09</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>252</v>
+      <c r="A10" s="12" t="s">
+        <v>253</v>
       </c>
       <c r="B10" s="53" t="n">
         <v>18.45</v>
@@ -13560,12 +13573,12 @@
         <v>20.57</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>254</v>
+      <c r="A11" s="12" t="s">
+        <v>255</v>
       </c>
       <c r="B11" s="35" t="n">
         <f aca="false">B6/B10</f>
@@ -13576,12 +13589,12 @@
         <v>32.3650947982499</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
-        <v>256</v>
+      <c r="A12" s="12" t="s">
+        <v>257</v>
       </c>
       <c r="B12" s="23" t="n">
         <v>0.35</v>
@@ -13590,12 +13603,12 @@
         <v>1.02</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
-        <v>258</v>
+      <c r="A13" s="12" t="s">
+        <v>259</v>
       </c>
       <c r="B13" s="53" t="n">
         <v>26.55</v>
@@ -13604,12 +13617,12 @@
         <v>15.67</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>260</v>
+      <c r="A14" s="12" t="s">
+        <v>261</v>
       </c>
       <c r="B14" s="53" t="n">
         <v>17.72</v>
@@ -13618,121 +13631,121 @@
         <v>7.43</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="A16" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>262</v>
+      <c r="A17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>263</v>
       </c>
       <c r="C17" s="41"/>
-      <c r="D17" s="9" t="s">
-        <v>244</v>
+      <c r="D17" s="10" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
-        <v>263</v>
+      <c r="A18" s="12" t="s">
+        <v>264</v>
       </c>
       <c r="B18" s="53" t="n">
         <v>19.1</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>265</v>
+      <c r="A19" s="12" t="s">
+        <v>266</v>
       </c>
       <c r="B19" s="53" t="n">
         <v>19.8</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>266</v>
+      <c r="A20" s="12" t="s">
+        <v>267</v>
       </c>
       <c r="B20" s="53" t="n">
         <v>19</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>267</v>
+      <c r="A21" s="12" t="s">
+        <v>268</v>
       </c>
       <c r="B21" s="53" t="n">
         <v>25.5</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
-        <v>268</v>
+      <c r="A22" s="12" t="s">
+        <v>269</v>
       </c>
       <c r="B22" s="53" t="n">
         <v>61.52</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
-        <v>270</v>
+      <c r="A23" s="12" t="s">
+        <v>271</v>
       </c>
       <c r="B23" s="53" t="n">
         <v>15.5</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>272</v>
+      <c r="A24" s="12" t="s">
+        <v>273</v>
       </c>
       <c r="B24" s="53" t="n">
         <v>12.63</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="A26" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>27</v>
       </c>
+      <c r="C26" s="11" t="s">
+        <v>28</v>
+      </c>
       <c r="D26" s="41"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>44</v>
+      <c r="A27" s="12" t="s">
+        <v>45</v>
       </c>
       <c r="B27" s="32" t="n">
         <f aca="false">B22</f>
@@ -13743,15 +13756,15 @@
         <v>15.5</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
-        <v>276</v>
+      <c r="A28" s="12" t="s">
+        <v>277</v>
       </c>
       <c r="B28" s="54" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C28" s="32" t="n">
         <f aca="false">B24</f>
@@ -13759,30 +13772,30 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
+      <c r="A30" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="10" t="s">
+      <c r="A31" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="B31" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>244</v>
+      <c r="C31" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
-        <v>279</v>
+      <c r="A32" s="12" t="s">
+        <v>280</v>
       </c>
       <c r="B32" s="55" t="n">
         <f aca="false">B9/$B$21-1</f>
@@ -13794,8 +13807,8 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
-        <v>280</v>
+      <c r="A33" s="12" t="s">
+        <v>281</v>
       </c>
       <c r="B33" s="55" t="n">
         <f aca="false">B9/B27-1</f>
@@ -13807,8 +13820,8 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>281</v>
+      <c r="A34" s="12" t="s">
+        <v>282</v>
       </c>
       <c r="B34" s="55" t="n">
         <f aca="false">B10/$B$18-1</f>
@@ -13820,8 +13833,8 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
-        <v>282</v>
+      <c r="A35" s="12" t="s">
+        <v>283</v>
       </c>
       <c r="B35" s="55" t="n">
         <f aca="false">B10/$B$20-1</f>
@@ -13833,8 +13846,8 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
-        <v>283</v>
+      <c r="A36" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="B36" s="55" t="str">
         <f aca="false">IF(ISNUMBER(B28),B10/B28-1,"n/a")</f>
@@ -13846,46 +13859,46 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
+      <c r="A38" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B39" s="10" t="s">
+      <c r="A39" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="B39" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>244</v>
+      <c r="C39" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="B40" s="12" t="n">
+      <c r="A40" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="B40" s="13" t="n">
         <f aca="false">NVDA!D58</f>
         <v>141.623455385411</v>
       </c>
-      <c r="C40" s="12" t="n">
+      <c r="C40" s="13" t="n">
         <f aca="false">META!D58</f>
         <v>456.843177782755</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
-        <v>287</v>
+      <c r="A41" s="12" t="s">
+        <v>288</v>
       </c>
       <c r="B41" s="32" t="n">
         <f aca="false">B40/B11</f>
@@ -13896,12 +13909,12 @@
         <v>14.1153047945794</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
-        <v>289</v>
+      <c r="A42" s="12" t="s">
+        <v>290</v>
       </c>
       <c r="B42" s="26" t="n">
         <f aca="false">B41/$B$18-1</f>
@@ -13914,24 +13927,24 @@
       <c r="D42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11" t="s">
-        <v>290</v>
-      </c>
-      <c r="B43" s="12" t="n">
+      <c r="A43" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="B43" s="13" t="n">
         <f aca="false">NVDA_PnL!M26</f>
         <v>9.87949456017954</v>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C43" s="13" t="n">
         <f aca="false">META_PnL!M26</f>
         <v>30.7981351981352</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
-        <v>292</v>
+      <c r="A44" s="12" t="s">
+        <v>293</v>
       </c>
       <c r="B44" s="32" t="n">
         <f aca="false">B6/B43</f>
@@ -13942,12 +13955,12 @@
         <v>21.6165685265357</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11" t="s">
-        <v>294</v>
+      <c r="A45" s="12" t="s">
+        <v>295</v>
       </c>
       <c r="B45" s="26" t="n">
         <f aca="false">B11/B43-1</f>
@@ -13958,12 +13971,12 @@
         <v>0.0508783921504949</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="s">
-        <v>296</v>
+      <c r="A46" s="12" t="s">
+        <v>297</v>
       </c>
       <c r="B46" s="32" t="n">
         <f aca="false">B40/B7</f>
@@ -13974,12 +13987,12 @@
         <v>17.2133827348438</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -14012,461 +14025,461 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="A4" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="9" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>27</v>
       </c>
+      <c r="D5" s="10" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C15" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C16" s="56" t="s">
+        <v>320</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>326</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>331</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>336</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>341</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="C21" s="56" t="s">
+        <v>346</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="11" t="s">
+      <c r="C25" s="56" t="s">
+        <v>352</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>356</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="C16" s="56" t="s">
-        <v>319</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="C27" s="56" t="s">
+        <v>359</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="C28" s="56" t="s">
+        <v>363</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>366</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="56" t="s">
+        <v>369</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>322</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="C17" s="56" t="s">
-        <v>325</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="C18" s="56" t="s">
-        <v>330</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="C19" s="56" t="s">
-        <v>335</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="C20" s="56" t="s">
-        <v>340</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="C21" s="56" t="s">
-        <v>345</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="C25" s="56" t="s">
-        <v>351</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="C26" s="56" t="s">
-        <v>355</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="C27" s="56" t="s">
-        <v>358</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="C28" s="56" t="s">
-        <v>362</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="C29" s="56" t="s">
-        <v>365</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="C30" s="56" t="s">
-        <v>368</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>370</v>
+      <c r="F30" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -14495,47 +14508,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="A4" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="9" t="s">
+      <c r="A5" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="C5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>379</v>
       </c>
+      <c r="F5" s="10" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
-        <v>380</v>
+      <c r="A6" s="12" t="s">
+        <v>381</v>
       </c>
       <c r="B6" s="57" t="n">
         <v>8</v>
@@ -14546,16 +14559,16 @@
       <c r="D6" s="58" t="n">
         <v>0.2</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>382</v>
       </c>
+      <c r="F6" s="4" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>383</v>
+      <c r="A7" s="12" t="s">
+        <v>384</v>
       </c>
       <c r="B7" s="57" t="n">
         <v>10</v>
@@ -14566,16 +14579,16 @@
       <c r="D7" s="58" t="n">
         <v>0.2</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>385</v>
       </c>
+      <c r="F7" s="4" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>386</v>
+      <c r="A8" s="12" t="s">
+        <v>387</v>
       </c>
       <c r="B8" s="57" t="n">
         <v>10</v>
@@ -14586,16 +14599,16 @@
       <c r="D8" s="58" t="n">
         <v>0.2</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>388</v>
       </c>
+      <c r="F8" s="4" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>389</v>
+      <c r="A9" s="12" t="s">
+        <v>390</v>
       </c>
       <c r="B9" s="57" t="n">
         <v>9</v>
@@ -14606,16 +14619,16 @@
       <c r="D9" s="58" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>391</v>
       </c>
+      <c r="F9" s="4" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>392</v>
+      <c r="A10" s="12" t="s">
+        <v>393</v>
       </c>
       <c r="B10" s="16" t="n">
         <f aca="false">MAX(1,MIN(10,ROUND(6+10*(NVDA!D58/NVDA!B5-1),0)))</f>
@@ -14628,13 +14641,13 @@
       <c r="D10" s="58" t="n">
         <v>0.2</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>393</v>
+      <c r="E10" s="4" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D11" s="59" t="n">
         <f aca="false">SUM(D6:D10)</f>
@@ -14642,8 +14655,8 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>39</v>
+      <c r="A13" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="B13" s="60" t="n">
         <f aca="false">SUMPRODUCT(B6:B10,$D$6:$D$10)/SUM($D$6:$D$10)*10</f>
@@ -14655,14 +14668,14 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
-        <v>395</v>
-      </c>
-      <c r="B14" s="11" t="str">
+      <c r="A14" s="12" t="s">
+        <v>396</v>
+      </c>
+      <c r="B14" s="12" t="str">
         <f aca="false">IF(B13&gt;=80,"Exceptional",IF(B13&gt;=65,"Strong",IF(B13&gt;=50,"Mixed","Weak")))</f>
         <v>Strong</v>
       </c>
-      <c r="C14" s="11" t="str">
+      <c r="C14" s="12" t="str">
         <f aca="false">IF(C13&gt;=80,"Exceptional",IF(C13&gt;=65,"Strong",IF(C13&gt;=50,"Mixed","Weak")))</f>
         <v>Mixed</v>
       </c>
